--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017094</v>
+        <v>125017097</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464176</v>
+        <v>464155</v>
       </c>
       <c r="R2" t="n">
-        <v>6773661</v>
+        <v>6773657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125014650</v>
+        <v>125017095</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464233</v>
+        <v>464196</v>
       </c>
       <c r="R3" t="n">
-        <v>6773796</v>
+        <v>6773680</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125012924</v>
+        <v>125014650</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464378</v>
+        <v>464233</v>
       </c>
       <c r="R4" t="n">
-        <v>6773635</v>
+        <v>6773796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017097</v>
+        <v>125017094</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464155</v>
+        <v>464176</v>
       </c>
       <c r="R6" t="n">
-        <v>6773657</v>
+        <v>6773661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012264</v>
+        <v>125012862</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464368</v>
+        <v>464378</v>
       </c>
       <c r="R7" t="n">
-        <v>6773653</v>
+        <v>6773635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125012862</v>
+        <v>125012338</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017098</v>
+        <v>125012264</v>
       </c>
       <c r="B9" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464170</v>
+        <v>464368</v>
       </c>
       <c r="R9" t="n">
-        <v>6773660</v>
+        <v>6773653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017095</v>
+        <v>125017098</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464196</v>
+        <v>464170</v>
       </c>
       <c r="R10" t="n">
-        <v>6773680</v>
+        <v>6773660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017096</v>
+        <v>125017090</v>
       </c>
       <c r="B11" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464222</v>
+        <v>464171</v>
       </c>
       <c r="R11" t="n">
-        <v>6773792</v>
+        <v>6773657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017090</v>
+        <v>125017096</v>
       </c>
       <c r="B12" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464171</v>
+        <v>464222</v>
       </c>
       <c r="R12" t="n">
-        <v>6773657</v>
+        <v>6773792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017097</v>
+        <v>125013129</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464155</v>
+        <v>464233</v>
       </c>
       <c r="R2" t="n">
-        <v>6773657</v>
+        <v>6773796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017095</v>
+        <v>125012924</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464196</v>
+        <v>464378</v>
       </c>
       <c r="R3" t="n">
-        <v>6773680</v>
+        <v>6773635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125014650</v>
+        <v>125017091</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464233</v>
+        <v>464189</v>
       </c>
       <c r="R4" t="n">
-        <v>6773796</v>
+        <v>6773669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017093</v>
+        <v>125017098</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464165</v>
+        <v>464170</v>
       </c>
       <c r="R5" t="n">
-        <v>6773652</v>
+        <v>6773660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017094</v>
+        <v>125012264</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464176</v>
+        <v>464368</v>
       </c>
       <c r="R6" t="n">
-        <v>6773661</v>
+        <v>6773653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012862</v>
+        <v>125017090</v>
       </c>
       <c r="B7" t="n">
         <v>79428</v>
@@ -1221,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464378</v>
+        <v>464171</v>
       </c>
       <c r="R7" t="n">
-        <v>6773635</v>
+        <v>6773657</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,11 +1263,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125012338</v>
+        <v>125017096</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464378</v>
+        <v>464222</v>
       </c>
       <c r="R8" t="n">
-        <v>6773635</v>
+        <v>6773792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125012264</v>
+        <v>125017097</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464368</v>
+        <v>464155</v>
       </c>
       <c r="R9" t="n">
-        <v>6773653</v>
+        <v>6773657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017098</v>
+        <v>125017095</v>
       </c>
       <c r="B10" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464170</v>
+        <v>464196</v>
       </c>
       <c r="R10" t="n">
-        <v>6773660</v>
+        <v>6773680</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017090</v>
+        <v>125017093</v>
       </c>
       <c r="B11" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464171</v>
+        <v>464165</v>
       </c>
       <c r="R11" t="n">
-        <v>6773657</v>
+        <v>6773652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017096</v>
+        <v>125017094</v>
       </c>
       <c r="B12" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464222</v>
+        <v>464176</v>
       </c>
       <c r="R12" t="n">
-        <v>6773792</v>
+        <v>6773661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017091</v>
+        <v>125012862</v>
       </c>
       <c r="B13" t="n">
         <v>79428</v>
@@ -1838,14 +1833,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464189</v>
+        <v>464378</v>
       </c>
       <c r="R13" t="n">
-        <v>6773669</v>
+        <v>6773635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,6 +1875,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1892,12 +1892,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017091</v>
+        <v>125017098</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464189</v>
+        <v>464170</v>
       </c>
       <c r="R4" t="n">
-        <v>6773669</v>
+        <v>6773660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017098</v>
+        <v>125017091</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464170</v>
+        <v>464189</v>
       </c>
       <c r="R5" t="n">
-        <v>6773660</v>
+        <v>6773669</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125013129</v>
+        <v>125017097</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464233</v>
+        <v>464155</v>
       </c>
       <c r="R2" t="n">
-        <v>6773796</v>
+        <v>6773657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125012924</v>
+        <v>125017096</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464378</v>
+        <v>464222</v>
       </c>
       <c r="R3" t="n">
-        <v>6773635</v>
+        <v>6773792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017098</v>
+        <v>125017094</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464170</v>
+        <v>464176</v>
       </c>
       <c r="R4" t="n">
-        <v>6773660</v>
+        <v>6773661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017091</v>
+        <v>125017098</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464189</v>
+        <v>464170</v>
       </c>
       <c r="R5" t="n">
-        <v>6773669</v>
+        <v>6773660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125012264</v>
+        <v>125014650</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464368</v>
+        <v>464233</v>
       </c>
       <c r="R6" t="n">
-        <v>6773653</v>
+        <v>6773796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017090</v>
+        <v>125012924</v>
       </c>
       <c r="B7" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464171</v>
+        <v>464378</v>
       </c>
       <c r="R7" t="n">
-        <v>6773657</v>
+        <v>6773635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017096</v>
+        <v>125017093</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464222</v>
+        <v>464165</v>
       </c>
       <c r="R8" t="n">
-        <v>6773792</v>
+        <v>6773652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017097</v>
+        <v>125012862</v>
       </c>
       <c r="B9" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464155</v>
+        <v>464378</v>
       </c>
       <c r="R9" t="n">
-        <v>6773657</v>
+        <v>6773635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,6 +1467,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1479,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017095</v>
+        <v>125017090</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464196</v>
+        <v>464171</v>
       </c>
       <c r="R10" t="n">
-        <v>6773680</v>
+        <v>6773657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017093</v>
+        <v>125017091</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464165</v>
+        <v>464189</v>
       </c>
       <c r="R11" t="n">
-        <v>6773652</v>
+        <v>6773669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017094</v>
+        <v>125017095</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464176</v>
+        <v>464196</v>
       </c>
       <c r="R12" t="n">
-        <v>6773661</v>
+        <v>6773680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125012862</v>
+        <v>125012264</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464378</v>
+        <v>464368</v>
       </c>
       <c r="R13" t="n">
-        <v>6773635</v>
+        <v>6773653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,11 +1878,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017097</v>
+        <v>125017096</v>
       </c>
       <c r="B2" t="n">
         <v>78455</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464155</v>
+        <v>464222</v>
       </c>
       <c r="R2" t="n">
-        <v>6773657</v>
+        <v>6773792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017096</v>
+        <v>125012264</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464222</v>
+        <v>464368</v>
       </c>
       <c r="R3" t="n">
-        <v>6773792</v>
+        <v>6773653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017098</v>
+        <v>125013052</v>
       </c>
       <c r="B5" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464170</v>
+        <v>464233</v>
       </c>
       <c r="R5" t="n">
-        <v>6773660</v>
+        <v>6773796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125014650</v>
+        <v>125012924</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464233</v>
+        <v>464378</v>
       </c>
       <c r="R6" t="n">
-        <v>6773796</v>
+        <v>6773635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012924</v>
+        <v>125017091</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464378</v>
+        <v>464189</v>
       </c>
       <c r="R7" t="n">
-        <v>6773635</v>
+        <v>6773669</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017093</v>
+        <v>125017090</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464165</v>
+        <v>464171</v>
       </c>
       <c r="R8" t="n">
-        <v>6773652</v>
+        <v>6773657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125012862</v>
+        <v>125017095</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464378</v>
+        <v>464196</v>
       </c>
       <c r="R9" t="n">
-        <v>6773635</v>
+        <v>6773680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,11 +1467,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1484,22 +1479,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017090</v>
+        <v>125017098</v>
       </c>
       <c r="B10" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464171</v>
+        <v>464170</v>
       </c>
       <c r="R10" t="n">
-        <v>6773657</v>
+        <v>6773660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017091</v>
+        <v>125012862</v>
       </c>
       <c r="B11" t="n">
         <v>79428</v>
@@ -1634,14 +1629,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464189</v>
+        <v>464378</v>
       </c>
       <c r="R11" t="n">
-        <v>6773669</v>
+        <v>6773635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,6 +1671,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,22 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017095</v>
+        <v>125017097</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464196</v>
+        <v>464155</v>
       </c>
       <c r="R12" t="n">
-        <v>6773680</v>
+        <v>6773657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125012264</v>
+        <v>125017093</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1838,14 +1838,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464368</v>
+        <v>464165</v>
       </c>
       <c r="R13" t="n">
-        <v>6773653</v>
+        <v>6773652</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,12 +1892,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017096</v>
+        <v>125017091</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464222</v>
+        <v>464189</v>
       </c>
       <c r="R2" t="n">
-        <v>6773792</v>
+        <v>6773669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125012264</v>
+        <v>125017096</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464368</v>
+        <v>464222</v>
       </c>
       <c r="R3" t="n">
-        <v>6773653</v>
+        <v>6773792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125013052</v>
+        <v>125012924</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464233</v>
+        <v>464378</v>
       </c>
       <c r="R5" t="n">
-        <v>6773796</v>
+        <v>6773635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125012924</v>
+        <v>125017090</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464378</v>
+        <v>464171</v>
       </c>
       <c r="R6" t="n">
-        <v>6773635</v>
+        <v>6773657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017091</v>
+        <v>125012264</v>
       </c>
       <c r="B7" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464189</v>
+        <v>464368</v>
       </c>
       <c r="R7" t="n">
-        <v>6773669</v>
+        <v>6773653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017090</v>
+        <v>125013129</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464171</v>
+        <v>464233</v>
       </c>
       <c r="R8" t="n">
-        <v>6773657</v>
+        <v>6773796</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017095</v>
+        <v>125017098</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464196</v>
+        <v>464170</v>
       </c>
       <c r="R9" t="n">
-        <v>6773680</v>
+        <v>6773660</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017098</v>
+        <v>125012862</v>
       </c>
       <c r="B10" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464170</v>
+        <v>464378</v>
       </c>
       <c r="R10" t="n">
-        <v>6773660</v>
+        <v>6773635</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,6 +1569,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1581,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125012862</v>
+        <v>125017093</v>
       </c>
       <c r="B11" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464378</v>
+        <v>464165</v>
       </c>
       <c r="R11" t="n">
-        <v>6773635</v>
+        <v>6773652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,11 +1676,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1688,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017093</v>
+        <v>125017095</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464165</v>
+        <v>464196</v>
       </c>
       <c r="R13" t="n">
-        <v>6773652</v>
+        <v>6773680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017091</v>
+        <v>125014650</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464189</v>
+        <v>464233</v>
       </c>
       <c r="R2" t="n">
-        <v>6773669</v>
+        <v>6773796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017096</v>
+        <v>125012862</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464222</v>
+        <v>464378</v>
       </c>
       <c r="R3" t="n">
-        <v>6773792</v>
+        <v>6773635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +855,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,19 +872,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017094</v>
+        <v>125012264</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -915,14 +920,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464176</v>
+        <v>464368</v>
       </c>
       <c r="R4" t="n">
-        <v>6773661</v>
+        <v>6773653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125012924</v>
+        <v>125017091</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464378</v>
+        <v>464189</v>
       </c>
       <c r="R5" t="n">
-        <v>6773635</v>
+        <v>6773669</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017090</v>
+        <v>125017098</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>78455</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464171</v>
+        <v>464170</v>
       </c>
       <c r="R6" t="n">
-        <v>6773657</v>
+        <v>6773660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012264</v>
+        <v>125017094</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1221,14 +1226,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464368</v>
+        <v>464176</v>
       </c>
       <c r="R7" t="n">
-        <v>6773653</v>
+        <v>6773661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,19 +1280,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125013129</v>
+        <v>125017093</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1323,14 +1328,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464233</v>
+        <v>464165</v>
       </c>
       <c r="R8" t="n">
-        <v>6773796</v>
+        <v>6773652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017098</v>
+        <v>125017095</v>
       </c>
       <c r="B9" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464170</v>
+        <v>464196</v>
       </c>
       <c r="R9" t="n">
-        <v>6773660</v>
+        <v>6773680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125012862</v>
+        <v>125012924</v>
       </c>
       <c r="B10" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,11 +1572,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017093</v>
+        <v>125017096</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464165</v>
+        <v>464222</v>
       </c>
       <c r="R11" t="n">
-        <v>6773652</v>
+        <v>6773792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017095</v>
+        <v>125017090</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464196</v>
+        <v>464171</v>
       </c>
       <c r="R13" t="n">
-        <v>6773680</v>
+        <v>6773657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125014650</v>
+        <v>125017091</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464233</v>
+        <v>464189</v>
       </c>
       <c r="R2" t="n">
-        <v>6773796</v>
+        <v>6773669</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125012862</v>
+        <v>125014650</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464378</v>
+        <v>464233</v>
       </c>
       <c r="R3" t="n">
-        <v>6773635</v>
+        <v>6773796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125012264</v>
+        <v>125017098</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464368</v>
+        <v>464170</v>
       </c>
       <c r="R4" t="n">
-        <v>6773653</v>
+        <v>6773660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017091</v>
+        <v>125012264</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464189</v>
+        <v>464368</v>
       </c>
       <c r="R5" t="n">
-        <v>6773669</v>
+        <v>6773653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017098</v>
+        <v>125017096</v>
       </c>
       <c r="B6" t="n">
         <v>78455</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464170</v>
+        <v>464222</v>
       </c>
       <c r="R6" t="n">
-        <v>6773660</v>
+        <v>6773792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017094</v>
+        <v>125012338</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1226,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464176</v>
+        <v>464378</v>
       </c>
       <c r="R7" t="n">
-        <v>6773661</v>
+        <v>6773635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017093</v>
+        <v>125012862</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464165</v>
+        <v>464378</v>
       </c>
       <c r="R8" t="n">
-        <v>6773652</v>
+        <v>6773635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,6 +1365,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1382,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017095</v>
+        <v>125017090</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464196</v>
+        <v>464171</v>
       </c>
       <c r="R9" t="n">
-        <v>6773680</v>
+        <v>6773657</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125012924</v>
+        <v>125017094</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1532,14 +1532,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464378</v>
+        <v>464176</v>
       </c>
       <c r="R10" t="n">
-        <v>6773635</v>
+        <v>6773661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,22 +1586,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017096</v>
+        <v>125017093</v>
       </c>
       <c r="B11" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464222</v>
+        <v>464165</v>
       </c>
       <c r="R11" t="n">
-        <v>6773792</v>
+        <v>6773652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017090</v>
+        <v>125017095</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464171</v>
+        <v>464196</v>
       </c>
       <c r="R13" t="n">
-        <v>6773657</v>
+        <v>6773680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017091</v>
+        <v>125014650</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464189</v>
+        <v>464233</v>
       </c>
       <c r="R2" t="n">
-        <v>6773669</v>
+        <v>6773796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125014650</v>
+        <v>125017097</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464233</v>
+        <v>464155</v>
       </c>
       <c r="R3" t="n">
-        <v>6773796</v>
+        <v>6773657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017098</v>
+        <v>125017094</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464170</v>
+        <v>464176</v>
       </c>
       <c r="R4" t="n">
-        <v>6773660</v>
+        <v>6773661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125012264</v>
+        <v>125012862</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464368</v>
+        <v>464378</v>
       </c>
       <c r="R5" t="n">
-        <v>6773653</v>
+        <v>6773635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017096</v>
+        <v>125017091</v>
       </c>
       <c r="B6" t="n">
-        <v>78455</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464222</v>
+        <v>464189</v>
       </c>
       <c r="R6" t="n">
-        <v>6773792</v>
+        <v>6773669</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012338</v>
+        <v>125012264</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464378</v>
+        <v>464368</v>
       </c>
       <c r="R7" t="n">
-        <v>6773635</v>
+        <v>6773653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125012862</v>
+        <v>125012924</v>
       </c>
       <c r="B8" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017090</v>
+        <v>125017093</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464171</v>
+        <v>464165</v>
       </c>
       <c r="R9" t="n">
-        <v>6773657</v>
+        <v>6773652</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017094</v>
+        <v>125017090</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464176</v>
+        <v>464171</v>
       </c>
       <c r="R10" t="n">
-        <v>6773661</v>
+        <v>6773657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017093</v>
+        <v>125017096</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464165</v>
+        <v>464222</v>
       </c>
       <c r="R11" t="n">
-        <v>6773652</v>
+        <v>6773792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017097</v>
+        <v>125017098</v>
       </c>
       <c r="B12" t="n">
         <v>78455</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464155</v>
+        <v>464170</v>
       </c>
       <c r="R12" t="n">
-        <v>6773657</v>
+        <v>6773660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017096</v>
+        <v>125017098</v>
       </c>
       <c r="B11" t="n">
         <v>78455</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464222</v>
+        <v>464170</v>
       </c>
       <c r="R11" t="n">
-        <v>6773792</v>
+        <v>6773660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017098</v>
+        <v>125017096</v>
       </c>
       <c r="B12" t="n">
         <v>78455</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464170</v>
+        <v>464222</v>
       </c>
       <c r="R12" t="n">
-        <v>6773660</v>
+        <v>6773792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125014650</v>
+        <v>125012264</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464233</v>
+        <v>464368</v>
       </c>
       <c r="R2" t="n">
-        <v>6773796</v>
+        <v>6773653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017097</v>
+        <v>125012924</v>
       </c>
       <c r="B3" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464155</v>
+        <v>464378</v>
       </c>
       <c r="R3" t="n">
-        <v>6773657</v>
+        <v>6773635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017094</v>
+        <v>125017096</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464176</v>
+        <v>464222</v>
       </c>
       <c r="R4" t="n">
-        <v>6773661</v>
+        <v>6773792</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125012862</v>
+        <v>125017093</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464378</v>
+        <v>464165</v>
       </c>
       <c r="R5" t="n">
-        <v>6773635</v>
+        <v>6773652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1059,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017091</v>
+        <v>125017090</v>
       </c>
       <c r="B6" t="n">
         <v>79428</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464189</v>
+        <v>464171</v>
       </c>
       <c r="R6" t="n">
-        <v>6773669</v>
+        <v>6773657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012264</v>
+        <v>125017095</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1226,14 +1221,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464368</v>
+        <v>464196</v>
       </c>
       <c r="R7" t="n">
-        <v>6773653</v>
+        <v>6773680</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125012924</v>
+        <v>125017097</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464378</v>
+        <v>464155</v>
       </c>
       <c r="R8" t="n">
-        <v>6773635</v>
+        <v>6773657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,19 +1377,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017093</v>
+        <v>125014650</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1430,14 +1425,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464165</v>
+        <v>464233</v>
       </c>
       <c r="R9" t="n">
-        <v>6773652</v>
+        <v>6773796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,19 +1479,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017090</v>
+        <v>125017091</v>
       </c>
       <c r="B10" t="n">
         <v>79428</v>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464171</v>
+        <v>464189</v>
       </c>
       <c r="R10" t="n">
-        <v>6773657</v>
+        <v>6773669</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017096</v>
+        <v>125017094</v>
       </c>
       <c r="B12" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464222</v>
+        <v>464176</v>
       </c>
       <c r="R12" t="n">
-        <v>6773792</v>
+        <v>6773661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017095</v>
+        <v>125012862</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464196</v>
+        <v>464378</v>
       </c>
       <c r="R13" t="n">
-        <v>6773680</v>
+        <v>6773635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,6 +1875,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1892,12 +1892,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125012264</v>
+        <v>125017093</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464368</v>
+        <v>464165</v>
       </c>
       <c r="R2" t="n">
-        <v>6773653</v>
+        <v>6773652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125012924</v>
+        <v>125013129</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464378</v>
+        <v>464233</v>
       </c>
       <c r="R3" t="n">
-        <v>6773635</v>
+        <v>6773796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017096</v>
+        <v>125017091</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>79565</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464222</v>
+        <v>464189</v>
       </c>
       <c r="R4" t="n">
-        <v>6773792</v>
+        <v>6773669</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017093</v>
+        <v>125017094</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464165</v>
+        <v>464176</v>
       </c>
       <c r="R5" t="n">
-        <v>6773652</v>
+        <v>6773661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017090</v>
+        <v>125012862</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464171</v>
+        <v>464378</v>
       </c>
       <c r="R6" t="n">
-        <v>6773657</v>
+        <v>6773635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,6 +1161,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1173,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017095</v>
+        <v>125012338</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,14 +1226,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464196</v>
+        <v>464378</v>
       </c>
       <c r="R7" t="n">
-        <v>6773680</v>
+        <v>6773635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017097</v>
+        <v>125017095</v>
       </c>
       <c r="B8" t="n">
-        <v>78455</v>
+        <v>78947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464155</v>
+        <v>464196</v>
       </c>
       <c r="R8" t="n">
-        <v>6773657</v>
+        <v>6773680</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125014650</v>
+        <v>125017098</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78592</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,34 +1410,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464233</v>
+        <v>464170</v>
       </c>
       <c r="R9" t="n">
-        <v>6773796</v>
+        <v>6773660</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017091</v>
+        <v>125017090</v>
       </c>
       <c r="B10" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464189</v>
+        <v>464171</v>
       </c>
       <c r="R10" t="n">
-        <v>6773669</v>
+        <v>6773657</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017098</v>
+        <v>125012264</v>
       </c>
       <c r="B11" t="n">
-        <v>78455</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464170</v>
+        <v>464368</v>
       </c>
       <c r="R11" t="n">
-        <v>6773660</v>
+        <v>6773653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,22 +1688,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017094</v>
+        <v>125017097</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78592</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464176</v>
+        <v>464155</v>
       </c>
       <c r="R12" t="n">
-        <v>6773661</v>
+        <v>6773657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125012862</v>
+        <v>125017096</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>78592</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1818,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464378</v>
+        <v>464222</v>
       </c>
       <c r="R13" t="n">
-        <v>6773635</v>
+        <v>6773792</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,11 +1880,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1892,12 +1892,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017093</v>
+        <v>125017097</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>78592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464165</v>
+        <v>464155</v>
       </c>
       <c r="R2" t="n">
-        <v>6773652</v>
+        <v>6773657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125013129</v>
+        <v>125017091</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464233</v>
+        <v>464189</v>
       </c>
       <c r="R3" t="n">
-        <v>6773796</v>
+        <v>6773669</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017091</v>
+        <v>125017094</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464189</v>
+        <v>464176</v>
       </c>
       <c r="R4" t="n">
-        <v>6773669</v>
+        <v>6773661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017094</v>
+        <v>125013129</v>
       </c>
       <c r="B5" t="n">
         <v>78947</v>
@@ -1017,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464176</v>
+        <v>464233</v>
       </c>
       <c r="R5" t="n">
-        <v>6773661</v>
+        <v>6773796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125012862</v>
+        <v>125017090</v>
       </c>
       <c r="B6" t="n">
         <v>79565</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464378</v>
+        <v>464171</v>
       </c>
       <c r="R6" t="n">
-        <v>6773635</v>
+        <v>6773657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,11 +1161,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,19 +1173,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012338</v>
+        <v>125012924</v>
       </c>
       <c r="B7" t="n">
         <v>78947</v>
@@ -1292,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017095</v>
+        <v>125012264</v>
       </c>
       <c r="B8" t="n">
         <v>78947</v>
@@ -1328,14 +1323,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464196</v>
+        <v>464368</v>
       </c>
       <c r="R8" t="n">
-        <v>6773680</v>
+        <v>6773653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017098</v>
+        <v>125017095</v>
       </c>
       <c r="B9" t="n">
-        <v>78592</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464170</v>
+        <v>464196</v>
       </c>
       <c r="R9" t="n">
-        <v>6773660</v>
+        <v>6773680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017090</v>
+        <v>125017098</v>
       </c>
       <c r="B10" t="n">
-        <v>79565</v>
+        <v>78592</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464171</v>
+        <v>464170</v>
       </c>
       <c r="R10" t="n">
-        <v>6773657</v>
+        <v>6773660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125012264</v>
+        <v>125017096</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>78592</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464368</v>
+        <v>464222</v>
       </c>
       <c r="R11" t="n">
-        <v>6773653</v>
+        <v>6773792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017097</v>
+        <v>125012862</v>
       </c>
       <c r="B12" t="n">
-        <v>78592</v>
+        <v>79565</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,34 +1711,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464155</v>
+        <v>464378</v>
       </c>
       <c r="R12" t="n">
-        <v>6773657</v>
+        <v>6773635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,6 +1773,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1790,22 +1790,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017096</v>
+        <v>125017093</v>
       </c>
       <c r="B13" t="n">
-        <v>78592</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464222</v>
+        <v>464165</v>
       </c>
       <c r="R13" t="n">
-        <v>6773792</v>
+        <v>6773652</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 20067-2025 artfynd.xlsx
+++ b/artfynd/A 20067-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017097</v>
+        <v>125013052</v>
       </c>
       <c r="B2" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464155</v>
+        <v>464233</v>
       </c>
       <c r="R2" t="n">
-        <v>6773657</v>
+        <v>6773796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017091</v>
+        <v>125012924</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464189</v>
+        <v>464378</v>
       </c>
       <c r="R3" t="n">
-        <v>6773669</v>
+        <v>6773635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017094</v>
+        <v>125012862</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464176</v>
+        <v>464378</v>
       </c>
       <c r="R4" t="n">
-        <v>6773661</v>
+        <v>6773635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,6 +942,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -969,27 +959,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125013129</v>
+        <v>125017091</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464233</v>
+        <v>464189</v>
       </c>
       <c r="R5" t="n">
-        <v>6773796</v>
+        <v>6773669</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,27 +1056,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017090</v>
+        <v>125017096</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464171</v>
+        <v>464222</v>
       </c>
       <c r="R6" t="n">
-        <v>6773657</v>
+        <v>6773792</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,16 +1165,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125012924</v>
+        <v>125017094</v>
       </c>
       <c r="B7" t="n">
         <v>78947</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1221,14 +1196,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464378</v>
+        <v>464176</v>
       </c>
       <c r="R7" t="n">
-        <v>6773635</v>
+        <v>6773661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,27 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125012264</v>
+        <v>125017098</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,34 +1273,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464368</v>
+        <v>464170</v>
       </c>
       <c r="R8" t="n">
-        <v>6773653</v>
+        <v>6773660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,28 +1347,23 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017095</v>
+        <v>125012264</v>
       </c>
       <c r="B9" t="n">
         <v>78947</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1425,14 +1390,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lingrovik, Dlr</t>
+          <t>Bjoset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464196</v>
+        <v>464368</v>
       </c>
       <c r="R9" t="n">
-        <v>6773680</v>
+        <v>6773653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,27 +1444,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017098</v>
+        <v>125017093</v>
       </c>
       <c r="B10" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464170</v>
+        <v>464165</v>
       </c>
       <c r="R10" t="n">
-        <v>6773660</v>
+        <v>6773652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,16 +1553,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017096</v>
+        <v>125017097</v>
       </c>
       <c r="B11" t="n">
         <v>78592</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1633,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464222</v>
+        <v>464155</v>
       </c>
       <c r="R11" t="n">
-        <v>6773792</v>
+        <v>6773657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,16 +1650,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125012862</v>
+        <v>125017090</v>
       </c>
       <c r="B12" t="n">
         <v>79565</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1731,14 +1681,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bjoset, Dlr</t>
+          <t>Lingrovik, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464378</v>
+        <v>464171</v>
       </c>
       <c r="R12" t="n">
-        <v>6773635</v>
+        <v>6773657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,11 +1723,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1790,28 +1735,23 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017093</v>
+        <v>125017095</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1842,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464165</v>
+        <v>464196</v>
       </c>
       <c r="R13" t="n">
-        <v>6773652</v>
+        <v>6773680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
